--- a/output/pdf_financials_xlsx/PCAA.P.xlsx
+++ b/output/pdf_financials_xlsx/PCAA.P.xlsx
@@ -695,13 +695,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.018478</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023099</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014107</v>
       </c>
     </row>
     <row r="13">
@@ -1053,13 +1053,13 @@
         <v>-0.044087</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.055849</v>
+        <v>-0.074327</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.04435</v>
+        <v>-0.067449</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.057205</v>
+        <v>-0.071312</v>
       </c>
     </row>
     <row r="28">
@@ -1097,13 +1097,13 @@
         <v>-0.044087</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.055849</v>
+        <v>-0.074327</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.04435</v>
+        <v>-0.067449</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.057205</v>
+        <v>-0.071312</v>
       </c>
     </row>
     <row r="30">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">

--- a/output/pdf_financials_xlsx/PCAA.P.xlsx
+++ b/output/pdf_financials_xlsx/PCAA.P.xlsx
@@ -2073,24 +2073,20 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.045163</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.007</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.014167</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.016165</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.01337</v>
       </c>
     </row>
     <row r="68">
@@ -2971,15 +2967,13 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.019415</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001929</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>-0.003252</v>
       </c>
     </row>
     <row r="102">
@@ -3097,13 +3091,13 @@
         <v>-0.009409000000000001</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.007163</v>
+        <v>0.012252</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.007738</v>
+        <v>-0.009667</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.002324</v>
+        <v>-0.005576</v>
       </c>
     </row>
     <row r="107">
@@ -5946,7 +5940,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -6533,7 +6531,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.255</v>
       </c>
